--- a/StudentFinalPresentation/XLSFormat/A7145_PresentationList.xlsx
+++ b/StudentFinalPresentation/XLSFormat/A7145_PresentationList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NeedDO\AZDNU\Projects\AI_Course\ai-management-course\StudentFinalPresentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NeedDO\AZDNU\Projects\AI_Course\ai-management-course\StudentFinalPresentation\XLSFormat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBA7917-2C6F-475F-9F29-E4710B69C62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D6C2CF-B9FB-47BC-9887-BBAEF4BD3073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5289D0CC-C038-484D-A6DE-0A92069F4E63}"/>
   </bookViews>
@@ -805,14 +805,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1191,6 +1191,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007CC1C6-B40C-4873-9FF1-6F2CEC114CA8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1208,11 +1211,11 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1239,7 +1242,7 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -1262,7 +1265,7 @@
       <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -1285,7 +1288,7 @@
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -1308,7 +1311,7 @@
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -1331,7 +1334,7 @@
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1354,7 +1357,7 @@
       <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1377,7 +1380,7 @@
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1400,7 +1403,7 @@
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1423,7 +1426,7 @@
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>75</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1446,7 +1449,7 @@
       <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1469,7 +1472,7 @@
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1492,7 +1495,7 @@
       <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1515,7 +1518,7 @@
       <c r="E14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1538,7 +1541,7 @@
       <c r="E15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1561,7 +1564,7 @@
       <c r="E16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1584,7 +1587,7 @@
       <c r="E17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -1607,7 +1610,7 @@
       <c r="E18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -1630,7 +1633,7 @@
       <c r="E19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -1653,7 +1656,7 @@
       <c r="E20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>83</v>
       </c>
       <c r="G20" s="3" t="s">
@@ -1676,7 +1679,7 @@
       <c r="E21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -1687,6 +1690,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>